--- a/result/grad/TotalData.xlsx
+++ b/result/grad/TotalData.xlsx
@@ -15,6 +15,54 @@
   <sheets>
     <sheet name="Total Data" sheetId="2" r:id="rId5"/>
     <sheet name="0103040030_op-21.plm.plx.xlsx" sheetId="3" r:id="rId6"/>
+    <sheet name="0104020007_op-20.plm.plx.xlsx" sheetId="4" r:id="rId7"/>
+    <sheet name="0104020009_OP-20.plm.plx.xlsx" sheetId="5" r:id="rId8"/>
+    <sheet name="0104020009_OP-21.plm.plx.xlsx" sheetId="6" r:id="rId9"/>
+    <sheet name="0903010030_op-21.plm.plx.xlsx" sheetId="7" r:id="rId10"/>
+    <sheet name="0903020030_op-21.plm.plx.xlsx" sheetId="8" r:id="rId11"/>
+    <sheet name="0903030031_OP-21.plm.plx.xlsx" sheetId="9" r:id="rId12"/>
+    <sheet name="0903030032_OP-20.plm.plx.xlsx" sheetId="10" r:id="rId13"/>
+    <sheet name="0903030033_OP-21.plm.plx.xlsx" sheetId="11" r:id="rId14"/>
+    <sheet name="0903030035_OP-21.plm.plx.xlsx" sheetId="12" r:id="rId15"/>
+    <sheet name="0903040030_op-21.plm.plx.xlsx" sheetId="13" r:id="rId16"/>
+    <sheet name="0904010001_OP-20.plm.plx.xlsx" sheetId="14" r:id="rId17"/>
+    <sheet name="0904010001_OP-21.plm.plx.xlsx" sheetId="15" r:id="rId18"/>
+    <sheet name="0904010003_OP-20.plm.plx.xlsx" sheetId="16" r:id="rId19"/>
+    <sheet name="0904010003_OP-21.plm.plx.xlsx" sheetId="17" r:id="rId20"/>
+    <sheet name="0904010004_OP-20.plm.plx.xlsx" sheetId="18" r:id="rId21"/>
+    <sheet name="0904010004_OP-21.plm.plx.xlsx" sheetId="19" r:id="rId22"/>
+    <sheet name="0904010006_OP-20.plm.plx.xlsx" sheetId="20" r:id="rId23"/>
+    <sheet name="0904010010_OP-20.plm.plx.xlsx" sheetId="21" r:id="rId24"/>
+    <sheet name="0904010010_OP-21.plm.plx.xlsx" sheetId="22" r:id="rId25"/>
+    <sheet name="0904010011_OP-21.plm.plx.xlsx" sheetId="23" r:id="rId26"/>
+    <sheet name="0904010012_OP-21.plm.plx.xlsx" sheetId="24" r:id="rId27"/>
+    <sheet name="0904020001_OP-20.plm.plx.xlsx" sheetId="25" r:id="rId28"/>
+    <sheet name="0904020001_OP-21.plm.plx.xlsx" sheetId="26" r:id="rId29"/>
+    <sheet name="0904020002_OP-20.plm.plx.xlsx" sheetId="27" r:id="rId30"/>
+    <sheet name="0904020002_OP-21.plm.plx.xlsx" sheetId="28" r:id="rId31"/>
+    <sheet name="0904020003_OP-20.plm.plx.xlsx" sheetId="29" r:id="rId32"/>
+    <sheet name="0904020003_OP-21.plm.plx.xlsx" sheetId="30" r:id="rId33"/>
+    <sheet name="0904020004_OP-20.plm.plx.xlsx" sheetId="31" r:id="rId34"/>
+    <sheet name="0904020004_OP-21.plm.plx.xlsx" sheetId="32" r:id="rId35"/>
+    <sheet name="0904020005_OP-20.plm.plx.xlsx" sheetId="33" r:id="rId36"/>
+    <sheet name="0904020005_OP-21.plm.plx.xlsx" sheetId="34" r:id="rId37"/>
+    <sheet name="0904020006_OP-20.plm.plx.xlsx" sheetId="35" r:id="rId38"/>
+    <sheet name="0904020006_OP-21.plm.plx.xlsx" sheetId="36" r:id="rId39"/>
+    <sheet name="0904040001_OP-20.plm.plx.xlsx" sheetId="37" r:id="rId40"/>
+    <sheet name="0904040002_OP-20.plm.plx.xlsx" sheetId="38" r:id="rId41"/>
+    <sheet name="0904040002_OP-21.plm.plx.xlsx" sheetId="39" r:id="rId42"/>
+    <sheet name="0904040003_OP-21.plm.plx.xlsx" sheetId="40" r:id="rId43"/>
+    <sheet name="1003010031_op-21.plm.plx.xlsx" sheetId="41" r:id="rId44"/>
+    <sheet name="1005010034_OP-21.pli.plx.xlsx" sheetId="42" r:id="rId45"/>
+    <sheet name="1005030035_OP-21.pli.plx.xlsx" sheetId="43" r:id="rId46"/>
+    <sheet name="1503040000_op-21.plm.plx.xlsx" sheetId="44" r:id="rId47"/>
+    <sheet name="2703030030_op-21.plm.plx.xlsx" sheetId="45" r:id="rId48"/>
+    <sheet name="2703040030_op-21.plm.plx.xlsx" sheetId="46" r:id="rId49"/>
+    <sheet name="2704030006_op-20.plm.plx.xlsx" sheetId="47" r:id="rId50"/>
+    <sheet name="2704030006_OP-21.plm..plx.xlsx" sheetId="48" r:id="rId51"/>
+    <sheet name="2704040001_OP-20.plm.plx.xlsx" sheetId="49" r:id="rId52"/>
+    <sheet name="2704040004_OP-20.plm.plx.xlsx" sheetId="50" r:id="rId53"/>
+    <sheet name="2704040005_OP-21.plm.plx.xlsx" sheetId="51" r:id="rId54"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -55,6 +103,150 @@
   </si>
   <si>
     <t>0103040030_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0104020007_op-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0104020009_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0104020009_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903010030_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903020030_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903030031_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903030032_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903030033_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903030035_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0903040030_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010001_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010001_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010003_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010003_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010004_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010004_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010006_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010010_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010010_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010011_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904010012_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020001_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020001_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020002_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020002_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020003_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020003_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020004_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020004_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020005_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020005_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020006_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904020006_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904040001_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904040002_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904040002_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>0904040003_OP-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>1003010031_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>1005010034_OP-21.pli.plx.xlsx</t>
+  </si>
+  <si>
+    <t>1005030035_OP-21.pli.plx.xlsx</t>
+  </si>
+  <si>
+    <t>1503040000_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>2703030030_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>2703040030_op-21.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>2704030006_op-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>2704030006_OP-21.plm..plx.xlsx</t>
+  </si>
+  <si>
+    <t>2704040001_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>2704040004_OP-20.plm.plx.xlsx</t>
+  </si>
+  <si>
+    <t>2704040005_OP-21.plm.plx.xlsx</t>
   </si>
 </sst>
 </file>
@@ -404,6 +596,96 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
@@ -443,11 +725,917 @@
         <v>63</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>124</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>136</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>124</v>
+      </c>
+      <c r="C4">
+        <v>23</v>
+      </c>
+      <c r="D4">
+        <v>130</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>124</v>
+      </c>
+      <c r="C5">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>130</v>
+      </c>
+      <c r="E5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>244</v>
+      </c>
+      <c r="C6">
+        <v>56</v>
+      </c>
+      <c r="D6">
+        <v>265</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>246</v>
+      </c>
+      <c r="C7">
+        <v>59</v>
+      </c>
+      <c r="D7">
+        <v>339</v>
+      </c>
+      <c r="E7">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>244</v>
+      </c>
+      <c r="C8">
+        <v>51</v>
+      </c>
+      <c r="D8">
+        <v>252</v>
+      </c>
+      <c r="E8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>244</v>
+      </c>
+      <c r="C9">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>257</v>
+      </c>
+      <c r="E9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>242</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>250</v>
+      </c>
+      <c r="E10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>255</v>
+      </c>
+      <c r="C11">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>263</v>
+      </c>
+      <c r="E11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <v>244</v>
+      </c>
+      <c r="C12">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <v>293</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
+        <v>124</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13">
+        <v>134</v>
+      </c>
+      <c r="E13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14">
+        <v>124</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>134</v>
+      </c>
+      <c r="E14">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
+        <v>124</v>
+      </c>
+      <c r="C15">
+        <v>25</v>
+      </c>
+      <c r="D15">
+        <v>134</v>
+      </c>
+      <c r="E15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
+        <v>124</v>
+      </c>
+      <c r="C16">
+        <v>25</v>
+      </c>
+      <c r="D16">
+        <v>134</v>
+      </c>
+      <c r="E16">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
+        <v>124</v>
+      </c>
+      <c r="C17">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <v>133</v>
+      </c>
+      <c r="E17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
+        <v>124</v>
+      </c>
+      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="D18">
+        <v>133</v>
+      </c>
+      <c r="E18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>124</v>
+      </c>
+      <c r="C19">
+        <v>25</v>
+      </c>
+      <c r="D19">
+        <v>133</v>
+      </c>
+      <c r="E19">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
+        <v>124</v>
+      </c>
+      <c r="C20">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>133</v>
+      </c>
+      <c r="E20">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>124</v>
+      </c>
+      <c r="C21">
+        <v>25</v>
+      </c>
+      <c r="D21">
+        <v>133</v>
+      </c>
+      <c r="E21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
+        <v>124</v>
+      </c>
+      <c r="C22">
+        <v>26</v>
+      </c>
+      <c r="D22">
+        <v>133</v>
+      </c>
+      <c r="E22">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
+        <v>124</v>
+      </c>
+      <c r="C23">
+        <v>22</v>
+      </c>
+      <c r="D23">
+        <v>130</v>
+      </c>
+      <c r="E23">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>124</v>
+      </c>
+      <c r="C24">
+        <v>26</v>
+      </c>
+      <c r="D24">
+        <v>136</v>
+      </c>
+      <c r="E24">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25">
+        <v>124</v>
+      </c>
+      <c r="C25">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>136</v>
+      </c>
+      <c r="E25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26">
+        <v>124</v>
+      </c>
+      <c r="C26">
+        <v>26</v>
+      </c>
+      <c r="D26">
+        <v>136</v>
+      </c>
+      <c r="E26">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27">
+        <v>124</v>
+      </c>
+      <c r="C27">
+        <v>26</v>
+      </c>
+      <c r="D27">
+        <v>136</v>
+      </c>
+      <c r="E27">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
+        <v>124</v>
+      </c>
+      <c r="C28">
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>136</v>
+      </c>
+      <c r="E28">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
+        <v>124</v>
+      </c>
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>136</v>
+      </c>
+      <c r="E29">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
+        <v>124</v>
+      </c>
+      <c r="C30">
+        <v>26</v>
+      </c>
+      <c r="D30">
+        <v>136</v>
+      </c>
+      <c r="E30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
+        <v>124</v>
+      </c>
+      <c r="C31">
+        <v>26</v>
+      </c>
+      <c r="D31">
+        <v>136</v>
+      </c>
+      <c r="E31">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
+        <v>124</v>
+      </c>
+      <c r="C32">
+        <v>26</v>
+      </c>
+      <c r="D32">
+        <v>136</v>
+      </c>
+      <c r="E32">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
+        <v>124</v>
+      </c>
+      <c r="C33">
+        <v>26</v>
+      </c>
+      <c r="D33">
+        <v>136</v>
+      </c>
+      <c r="E33">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
+        <v>124</v>
+      </c>
+      <c r="C34">
+        <v>26</v>
+      </c>
+      <c r="D34">
+        <v>136</v>
+      </c>
+      <c r="E34">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
+        <v>124</v>
+      </c>
+      <c r="C35">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>136</v>
+      </c>
+      <c r="E35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
+        <v>124</v>
+      </c>
+      <c r="C36">
+        <v>21</v>
+      </c>
+      <c r="D36">
+        <v>137</v>
+      </c>
+      <c r="E36">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
+        <v>124</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>137</v>
+      </c>
+      <c r="E37">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38">
+        <v>124</v>
+      </c>
+      <c r="C38">
+        <v>20</v>
+      </c>
+      <c r="D38">
+        <v>137</v>
+      </c>
+      <c r="E38">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39">
+        <v>124</v>
+      </c>
+      <c r="C39">
+        <v>22</v>
+      </c>
+      <c r="D39">
+        <v>128</v>
+      </c>
+      <c r="E39">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40">
+        <v>244</v>
+      </c>
+      <c r="C40">
+        <v>59</v>
+      </c>
+      <c r="D40">
+        <v>250</v>
+      </c>
+      <c r="E40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41">
+        <v>334</v>
+      </c>
+      <c r="C41">
+        <v>71</v>
+      </c>
+      <c r="D41">
+        <v>340</v>
+      </c>
+      <c r="E41">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42">
+        <v>334</v>
+      </c>
+      <c r="C42">
+        <v>72</v>
+      </c>
+      <c r="D42">
+        <v>340</v>
+      </c>
+      <c r="E42">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43">
+        <v>244</v>
+      </c>
+      <c r="C43">
+        <v>52</v>
+      </c>
+      <c r="D43">
+        <v>276</v>
+      </c>
+      <c r="E43">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44">
+        <v>245</v>
+      </c>
+      <c r="C44">
+        <v>51</v>
+      </c>
+      <c r="D44">
+        <v>265</v>
+      </c>
+      <c r="E44">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45">
+        <v>244</v>
+      </c>
+      <c r="C45">
+        <v>51</v>
+      </c>
+      <c r="D45">
+        <v>259</v>
+      </c>
+      <c r="E45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46">
+        <v>125</v>
+      </c>
+      <c r="C46">
+        <v>24</v>
+      </c>
+      <c r="D46">
+        <v>138</v>
+      </c>
+      <c r="E46">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47">
+        <v>125</v>
+      </c>
+      <c r="C47">
+        <v>27</v>
+      </c>
+      <c r="D47">
+        <v>131</v>
+      </c>
+      <c r="E47">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48">
+        <v>124</v>
+      </c>
+      <c r="C48">
+        <v>20</v>
+      </c>
+      <c r="D48">
+        <v>149</v>
+      </c>
+      <c r="E48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49">
+        <v>124</v>
+      </c>
+      <c r="C49">
+        <v>21</v>
+      </c>
+      <c r="D49">
+        <v>146</v>
+      </c>
+      <c r="E49">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50">
+        <v>124</v>
+      </c>
+      <c r="C50">
+        <v>25</v>
+      </c>
+      <c r="D50">
+        <v>142</v>
+      </c>
+      <c r="E50">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
@@ -455,4 +1643,256 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>